--- a/results/feature_selection/global_ind/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP_calc/metrics_global.xlsx
@@ -488,235 +488,235 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3864974565297001</v>
+        <v>0.938991689254779</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002963100643535995</v>
+        <v>0.001418290938936806</v>
       </c>
       <c r="F2" t="n">
-        <v>2.924758311614265e-05</v>
+        <v>3.010317618676656e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00540810346758849</v>
+        <v>0.001735026691055978</v>
       </c>
       <c r="H2" t="n">
-        <v>348.7576103864572</v>
+        <v>485.2081787656239</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1860712363492713</v>
+        <v>0.01980460044589936</v>
       </c>
       <c r="J2" t="n">
-        <v>-555.7445352752468</v>
+        <v>-655.1001781080018</v>
       </c>
       <c r="K2" t="n">
-        <v>-547.7885990889897</v>
+        <v>-649.2464469522575</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, dXdt_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2555640608870337</v>
+        <v>0.9389035686552867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004055531292104167</v>
+        <v>0.001405368876622691</v>
       </c>
       <c r="F3" t="n">
-        <v>3.548958718360104e-05</v>
+        <v>3.014665731089208e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005957313755678899</v>
+        <v>0.001736279277964581</v>
       </c>
       <c r="H3" t="n">
-        <v>1387.635304233258</v>
+        <v>464.777750681538</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2253556244449184</v>
+        <v>0.01983103966942576</v>
       </c>
       <c r="J3" t="n">
-        <v>-545.2986460571778</v>
+        <v>-655.025123333049</v>
       </c>
       <c r="K3" t="n">
-        <v>-537.3427098709208</v>
+        <v>-649.1713921773047</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2446404048236652</v>
+        <v>0.7742025612994408</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002924466005405861</v>
+        <v>0.002338217739991702</v>
       </c>
       <c r="F4" t="n">
-        <v>3.601035199875293e-05</v>
+        <v>1.11414658047322e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006000862604555525</v>
+        <v>0.003337883431866997</v>
       </c>
       <c r="H4" t="n">
-        <v>834.5553830190116</v>
+        <v>1194.901608192472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2291330857992996</v>
+        <v>0.0692470306362311</v>
       </c>
       <c r="J4" t="n">
-        <v>-542.5120216874644</v>
+        <v>-587.0515110938077</v>
       </c>
       <c r="K4" t="n">
-        <v>-532.5671014546431</v>
+        <v>-581.1977799380634</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2105905684402396</v>
+        <v>0.7736050041023355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003090907978317201</v>
+        <v>0.002435599077615304</v>
       </c>
       <c r="F5" t="n">
-        <v>3.76336140867666e-05</v>
+        <v>1.117095091809857e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006134624200940642</v>
+        <v>0.00334229725160683</v>
       </c>
       <c r="H5" t="n">
-        <v>771.2900629898285</v>
+        <v>1181.712448787595</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2388491729977889</v>
+        <v>0.06842631843494204</v>
       </c>
       <c r="J5" t="n">
-        <v>-542.131097424669</v>
+        <v>-590.9140784878666</v>
       </c>
       <c r="K5" t="n">
-        <v>-534.1751612384119</v>
+        <v>-588.9628347692852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T, V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1728456618950409</v>
+        <v>0.7624289190696809</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004948773517247461</v>
+        <v>0.002415580660709869</v>
       </c>
       <c r="F6" t="n">
-        <v>3.943303171451956e-05</v>
+        <v>1.172240965004295e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006279572574190027</v>
+        <v>0.003423800468783622</v>
       </c>
       <c r="H6" t="n">
-        <v>1974.906593716287</v>
+        <v>979.8885188720805</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2496739045536879</v>
+        <v>0.07177952996585077</v>
       </c>
       <c r="J6" t="n">
-        <v>-541.6089631233266</v>
+        <v>-588.4084260572683</v>
       </c>
       <c r="K6" t="n">
-        <v>-535.6420109836338</v>
+        <v>-586.4571823386869</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T, FS_calc, V_calc, Xlag1_calc</t>
+          <t>P, T</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1314979729767644</v>
+        <v>0.7450861526444962</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003164087736447099</v>
+        <v>0.002735441065643572</v>
       </c>
       <c r="F7" t="n">
-        <v>4.140420523477449e-05</v>
+        <v>1.257814937941117e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006434609952030853</v>
+        <v>0.003546568676821467</v>
       </c>
       <c r="H7" t="n">
-        <v>735.6190236447395</v>
+        <v>1586.391974597117</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2625795910506351</v>
+        <v>0.07748295891121675</v>
       </c>
       <c r="J7" t="n">
-        <v>-536.974917754903</v>
+        <v>-582.7445701347547</v>
       </c>
       <c r="K7" t="n">
-        <v>-529.0189815686459</v>
+        <v>-578.8420826975918</v>
       </c>
     </row>
     <row r="8">
@@ -730,77 +730,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08485662944145966</v>
+        <v>0.0907519038044583</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006110231336237772</v>
+        <v>0.005832034825113502</v>
       </c>
       <c r="F8" t="n">
-        <v>5.17185051250297e-05</v>
+        <v>4.486479842322231e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007191557906672913</v>
+        <v>0.006698119021279206</v>
       </c>
       <c r="H8" t="n">
-        <v>2709.2420010745</v>
+        <v>3655.035353477265</v>
       </c>
       <c r="I8" t="n">
-        <v>0.652986383572051</v>
+        <v>0.2738058342175588</v>
       </c>
       <c r="J8" t="n">
-        <v>-528.9635250161605</v>
+        <v>-516.6165676497335</v>
       </c>
       <c r="K8" t="n">
-        <v>-524.9855569230319</v>
+        <v>-512.7140802125706</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1571323220360512</v>
+        <v>0.07615652691839214</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003345297594433739</v>
+        <v>0.005922934414584713</v>
       </c>
       <c r="F9" t="n">
-        <v>5.516411321408472e-05</v>
+        <v>4.558497440670162e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007427254756239664</v>
+        <v>0.006751664565623918</v>
       </c>
       <c r="H9" t="n">
-        <v>574.5343653545675</v>
+        <v>3681.037533261998</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6953566229801305</v>
+        <v>0.2781849514065671</v>
       </c>
       <c r="J9" t="n">
-        <v>-527.4806887079454</v>
+        <v>-515.7884850271773</v>
       </c>
       <c r="K9" t="n">
-        <v>-525.4917046613812</v>
+        <v>-511.8859975900145</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FS_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1861314454813432</v>
+        <v>-0.4077372259495444</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003532314715513494</v>
+        <v>0.007798863440071049</v>
       </c>
       <c r="F10" t="n">
-        <v>5.654659203554785e-05</v>
+        <v>6.946162124436257e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007519746806611766</v>
+        <v>0.00833436387760713</v>
       </c>
       <c r="H10" t="n">
-        <v>595.100013169383</v>
+        <v>4418.818308118485</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7127580325176558</v>
+        <v>0.8457395818394688</v>
       </c>
       <c r="J10" t="n">
-        <v>-526.1440635794415</v>
+        <v>-495.8862808519719</v>
       </c>
       <c r="K10" t="n">
-        <v>-524.1550795328773</v>
+        <v>-493.9350371333905</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP_calc/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP_calc/metrics_global.xlsx
@@ -488,40 +488,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.938991689254779</v>
+        <v>0.3870190833708521</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001418290938936806</v>
+        <v>0.003006591422353727</v>
       </c>
       <c r="F2" t="n">
-        <v>3.010317618676656e-06</v>
+        <v>3.024616205072858e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001735026691055978</v>
+        <v>0.00549965108445332</v>
       </c>
       <c r="H2" t="n">
-        <v>485.2081787656239</v>
+        <v>358.4722741348548</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01980460044589936</v>
+        <v>0.1859154473021799</v>
       </c>
       <c r="J2" t="n">
-        <v>-655.1001781080018</v>
+        <v>-533.1193453064222</v>
       </c>
       <c r="K2" t="n">
-        <v>-649.2464469522575</v>
+        <v>-525.3143704320966</v>
       </c>
     </row>
     <row r="3">
@@ -531,159 +531,159 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9389035686552867</v>
+        <v>0.2409293520705205</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001405368876622691</v>
+        <v>0.003018518164432886</v>
       </c>
       <c r="F3" t="n">
-        <v>3.014665731089208e-06</v>
+        <v>3.745463064573135e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001736279277964581</v>
+        <v>0.006120018843576492</v>
       </c>
       <c r="H3" t="n">
-        <v>464.777750681538</v>
+        <v>866.3572116652292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01983103966942576</v>
+        <v>0.2302474126202959</v>
       </c>
       <c r="J3" t="n">
-        <v>-655.025123333049</v>
+        <v>-520.0037707584751</v>
       </c>
       <c r="K3" t="n">
-        <v>-649.1713921773047</v>
+        <v>-510.2475521655679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P, Plag1, Xlag1_calc</t>
+          <t>T, FS_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7742025612994408</v>
+        <v>0.2133252802024272</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002338217739991702</v>
+        <v>0.003126499883612591</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11414658047322e-05</v>
+        <v>3.881669136953595e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003337883431866997</v>
+        <v>0.006230304275838858</v>
       </c>
       <c r="H4" t="n">
-        <v>1194.901608192472</v>
+        <v>773.2633457827678</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0692470306362311</v>
+        <v>0.2380295876232305</v>
       </c>
       <c r="J4" t="n">
-        <v>-587.0515110938077</v>
+        <v>-520.1463311229932</v>
       </c>
       <c r="K4" t="n">
-        <v>-581.1977799380634</v>
+        <v>-512.3413562486675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7736050041023355</v>
+        <v>0.2096476384912143</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002435599077615304</v>
+        <v>0.004822983382772903</v>
       </c>
       <c r="F5" t="n">
-        <v>1.117095091809857e-05</v>
+        <v>3.899815631264308e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00334229725160683</v>
+        <v>0.006244850383527461</v>
       </c>
       <c r="H5" t="n">
-        <v>1181.712448787595</v>
+        <v>1963.897769276801</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06842631843494204</v>
+        <v>0.2386330071620546</v>
       </c>
       <c r="J5" t="n">
-        <v>-590.9140784878666</v>
+        <v>-521.9038017233174</v>
       </c>
       <c r="K5" t="n">
-        <v>-588.9628347692852</v>
+        <v>-516.0500705675731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, FS_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7624289190696809</v>
+        <v>0.135823533571047</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002415580660709869</v>
+        <v>0.003221657426833613</v>
       </c>
       <c r="F6" t="n">
-        <v>1.172240965004295e-05</v>
+        <v>4.264084041599873e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003423800468783622</v>
+        <v>0.00652999543767059</v>
       </c>
       <c r="H6" t="n">
-        <v>979.8885188720805</v>
+        <v>743.4480864997898</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07177952996585077</v>
+        <v>0.2612827885169771</v>
       </c>
       <c r="J6" t="n">
-        <v>-588.4084260572683</v>
+        <v>-515.2602995740882</v>
       </c>
       <c r="K6" t="n">
-        <v>-586.4571823386869</v>
+        <v>-507.4553246997625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -691,32 +691,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T</t>
+          <t>T, V_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7450861526444962</v>
+        <v>-0.0176384957608855</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002735441065643572</v>
+        <v>0.005657712420508166</v>
       </c>
       <c r="F7" t="n">
-        <v>1.257814937941117e-05</v>
+        <v>5.021307844476508e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003546568676821467</v>
+        <v>0.007086118715119377</v>
       </c>
       <c r="H7" t="n">
-        <v>1586.391974597117</v>
+        <v>1918.798026895999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07748295891121675</v>
+        <v>0.612653395766354</v>
       </c>
       <c r="J7" t="n">
-        <v>-582.7445701347547</v>
+        <v>-510.7602219973019</v>
       </c>
       <c r="K7" t="n">
-        <v>-578.8420826975918</v>
+        <v>-506.857734560139</v>
       </c>
     </row>
     <row r="8">
@@ -730,77 +730,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>X_calc, V_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.0907519038044583</v>
+        <v>-0.07573204844017578</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005832034825113502</v>
+        <v>0.00611940176075395</v>
       </c>
       <c r="F8" t="n">
-        <v>4.486479842322231e-05</v>
+        <v>5.307957389474235e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006698119021279206</v>
+        <v>0.007285572997008702</v>
       </c>
       <c r="H8" t="n">
-        <v>3655.035353477265</v>
+        <v>2856.323788247617</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2738058342175588</v>
+        <v>0.6475135404675582</v>
       </c>
       <c r="J8" t="n">
-        <v>-516.6165676497335</v>
+        <v>-507.873355559134</v>
       </c>
       <c r="K8" t="n">
-        <v>-512.7140802125706</v>
+        <v>-503.9708681219711</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.07615652691839214</v>
+        <v>-0.1914814749226239</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005922934414584713</v>
+        <v>0.003654563583581994</v>
       </c>
       <c r="F9" t="n">
-        <v>4.558497440670162e-05</v>
+        <v>5.879096851681197e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006751664565623918</v>
+        <v>0.007667526883996689</v>
       </c>
       <c r="H9" t="n">
-        <v>3681.037533261998</v>
+        <v>615.4195423991011</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2781849514065671</v>
+        <v>0.715971192309498</v>
       </c>
       <c r="J9" t="n">
-        <v>-515.7884850271773</v>
+        <v>-504.5591601985057</v>
       </c>
       <c r="K9" t="n">
-        <v>-511.8859975900145</v>
+        <v>-502.6079164799242</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>FS_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4077372259495444</v>
+        <v>-0.2154101378383779</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007798863440071049</v>
+        <v>0.003507240330793119</v>
       </c>
       <c r="F10" t="n">
-        <v>6.946162124436257e-05</v>
+        <v>5.997167446796481e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00833436387760713</v>
+        <v>0.007744138071339174</v>
       </c>
       <c r="H10" t="n">
-        <v>4418.818308118485</v>
+        <v>575.3745927143052</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8457395818394688</v>
+        <v>0.730330043047282</v>
       </c>
       <c r="J10" t="n">
-        <v>-495.8862808519719</v>
+        <v>-503.5251863694951</v>
       </c>
       <c r="K10" t="n">
-        <v>-493.9350371333905</v>
+        <v>-501.5739426509137</v>
       </c>
     </row>
   </sheetData>
